--- a/assignment3/data/trainingdataset_ontario_budgets_v22_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v22_llm_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EBE7DB-1CB1-7F4F-9AB0-9753FA1294F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE9C857-885E-A143-AFEC-284BA432F732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="1140" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="9140" yWindow="720" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4436,7 +4436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4489,19 +4489,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15810,7 +15804,7 @@
       <c r="B242" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="C242" s="24" t="s">
+      <c r="C242" t="s">
         <v>543</v>
       </c>
       <c r="F242" s="13">
@@ -16570,7 +16564,7 @@
       <c r="B262" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C262" s="27" t="s">
+      <c r="C262" s="26" t="s">
         <v>586</v>
       </c>
       <c r="F262" s="13">
@@ -16988,7 +16982,7 @@
       <c r="B273" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="C273" s="26" t="s">
+      <c r="C273" s="25" t="s">
         <v>611</v>
       </c>
       <c r="F273" s="13">
@@ -17026,7 +17020,7 @@
       <c r="B274" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C274" s="25" t="s">
+      <c r="C274" s="24" t="s">
         <v>612</v>
       </c>
       <c r="F274" s="13">
@@ -17064,7 +17058,7 @@
       <c r="B275" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="C275" s="26" t="s">
+      <c r="C275" s="25" t="s">
         <v>617</v>
       </c>
       <c r="F275" s="13">
@@ -17102,7 +17096,7 @@
       <c r="B276" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="C276" s="26" t="s">
+      <c r="C276" s="25" t="s">
         <v>618</v>
       </c>
       <c r="F276" s="13">
@@ -17140,7 +17134,7 @@
       <c r="B277" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C277" s="26" t="s">
+      <c r="C277" s="25" t="s">
         <v>619</v>
       </c>
       <c r="F277" s="13">
@@ -17178,7 +17172,7 @@
       <c r="B278" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C278" s="26" t="s">
+      <c r="C278" s="25" t="s">
         <v>625</v>
       </c>
       <c r="F278" s="13">
@@ -17213,7 +17207,7 @@
       <c r="B279" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="C279" s="24" t="s">
+      <c r="C279" t="s">
         <v>626</v>
       </c>
       <c r="F279" s="13">
@@ -17251,7 +17245,7 @@
       <c r="B280" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="C280" s="26" t="s">
+      <c r="C280" s="25" t="s">
         <v>628</v>
       </c>
       <c r="F280" s="13">
@@ -17286,7 +17280,7 @@
       <c r="B281" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C281" s="26" t="s">
+      <c r="C281" s="25" t="s">
         <v>629</v>
       </c>
       <c r="F281" s="13">
@@ -17321,7 +17315,7 @@
       <c r="B282" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="C282" s="26" t="s">
+      <c r="C282" s="25" t="s">
         <v>630</v>
       </c>
       <c r="F282" s="13">
@@ -17356,7 +17350,7 @@
       <c r="B283" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="C283" s="26" t="s">
+      <c r="C283" s="25" t="s">
         <v>631</v>
       </c>
       <c r="F283" s="13">
@@ -17391,7 +17385,7 @@
       <c r="B284" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="C284" s="26" t="s">
+      <c r="C284" s="25" t="s">
         <v>632</v>
       </c>
       <c r="F284" s="13">
@@ -17429,7 +17423,7 @@
       <c r="B285" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C285" s="26" t="s">
+      <c r="C285" s="25" t="s">
         <v>633</v>
       </c>
       <c r="F285" s="13">
@@ -17467,7 +17461,7 @@
       <c r="B286" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C286" s="26" t="s">
+      <c r="C286" s="25" t="s">
         <v>634</v>
       </c>
       <c r="F286" s="13">
@@ -17505,7 +17499,7 @@
       <c r="B287" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="C287" s="26" t="s">
+      <c r="C287" s="25" t="s">
         <v>635</v>
       </c>
       <c r="F287" s="13">
@@ -17543,7 +17537,7 @@
       <c r="B288" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="C288" s="29" t="s">
+      <c r="C288" s="9" t="s">
         <v>636</v>
       </c>
       <c r="F288" s="13">
@@ -17581,7 +17575,7 @@
       <c r="B289" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="C289" s="26" t="s">
+      <c r="C289" s="25" t="s">
         <v>648</v>
       </c>
       <c r="F289" s="13">
@@ -17616,7 +17610,7 @@
       <c r="B290" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="C290" s="26" t="s">
+      <c r="C290" s="25" t="s">
         <v>650</v>
       </c>
       <c r="F290" s="13">
@@ -17654,7 +17648,7 @@
       <c r="B291" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="C291" s="26" t="s">
+      <c r="C291" s="25" t="s">
         <v>652</v>
       </c>
       <c r="F291" s="13">
@@ -17692,7 +17686,7 @@
       <c r="B292" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="C292" s="26" t="s">
+      <c r="C292" s="25" t="s">
         <v>654</v>
       </c>
       <c r="F292" s="13">
@@ -17727,7 +17721,7 @@
       <c r="B293" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C293" s="26" t="s">
+      <c r="C293" s="25" t="s">
         <v>656</v>
       </c>
       <c r="F293" s="13">
@@ -17762,7 +17756,7 @@
       <c r="B294" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="C294" s="26" t="s">
+      <c r="C294" s="25" t="s">
         <v>657</v>
       </c>
       <c r="F294" s="13">
@@ -17797,7 +17791,7 @@
       <c r="B295" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="C295" s="26" t="s">
+      <c r="C295" s="25" t="s">
         <v>662</v>
       </c>
       <c r="F295" s="13">
@@ -17832,7 +17826,7 @@
       <c r="B296" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="C296" s="26" t="s">
+      <c r="C296" s="25" t="s">
         <v>663</v>
       </c>
       <c r="F296" s="13">
@@ -17867,7 +17861,7 @@
       <c r="B297" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="C297" s="26" t="s">
+      <c r="C297" s="25" t="s">
         <v>664</v>
       </c>
       <c r="F297" s="13">
@@ -17905,7 +17899,7 @@
       <c r="B298" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C298" s="28" t="s">
+      <c r="C298" s="25" t="s">
         <v>665</v>
       </c>
       <c r="F298" s="13">
@@ -17940,7 +17934,7 @@
       <c r="B299" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="C299" s="28" t="s">
+      <c r="C299" s="25" t="s">
         <v>666</v>
       </c>
       <c r="F299" s="13">
@@ -17975,7 +17969,7 @@
       <c r="B300" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="C300" s="28" t="s">
+      <c r="C300" s="25" t="s">
         <v>667</v>
       </c>
       <c r="F300" s="13">
@@ -18013,7 +18007,7 @@
       <c r="B301" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C301" s="28" t="s">
+      <c r="C301" s="25" t="s">
         <v>668</v>
       </c>
       <c r="F301" s="13">
@@ -18048,7 +18042,7 @@
       <c r="B302" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C302" s="28" t="s">
+      <c r="C302" s="25" t="s">
         <v>669</v>
       </c>
       <c r="F302" s="13">
@@ -18083,7 +18077,7 @@
       <c r="B303" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="C303" s="28" t="s">
+      <c r="C303" s="25" t="s">
         <v>679</v>
       </c>
       <c r="F303" s="13">
@@ -18118,7 +18112,7 @@
       <c r="B304" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="C304" s="28" t="s">
+      <c r="C304" s="25" t="s">
         <v>681</v>
       </c>
       <c r="F304" s="13">
@@ -18153,7 +18147,7 @@
       <c r="B305" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C305" s="24" t="s">
+      <c r="C305" t="s">
         <v>682</v>
       </c>
       <c r="F305" s="13">
@@ -18188,7 +18182,7 @@
       <c r="B306" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="C306" s="28" t="s">
+      <c r="C306" s="25" t="s">
         <v>683</v>
       </c>
       <c r="F306" s="13">
@@ -18226,7 +18220,7 @@
       <c r="B307" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="C307" s="24" t="s">
+      <c r="C307" t="s">
         <v>684</v>
       </c>
       <c r="F307" s="13">
@@ -18261,7 +18255,7 @@
       <c r="B308" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="C308" s="28" t="s">
+      <c r="C308" s="25" t="s">
         <v>685</v>
       </c>
       <c r="F308" s="13">
@@ -18296,7 +18290,7 @@
       <c r="B309" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="C309" s="24" t="s">
+      <c r="C309" t="s">
         <v>692</v>
       </c>
       <c r="F309" s="13">
@@ -18306,7 +18300,7 @@
         <v>1</v>
       </c>
       <c r="J309" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K309" s="4" t="s">
         <v>728</v>
@@ -18331,7 +18325,7 @@
       <c r="B310" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C310" s="24" t="s">
+      <c r="C310" t="s">
         <v>693</v>
       </c>
       <c r="F310" s="13">
@@ -18341,7 +18335,7 @@
         <v>2</v>
       </c>
       <c r="J310" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K310" s="4" t="s">
         <v>728</v>
@@ -18366,7 +18360,7 @@
       <c r="B311" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="C311" s="24" t="s">
+      <c r="C311" t="s">
         <v>694</v>
       </c>
       <c r="F311" s="13">
@@ -18376,7 +18370,7 @@
         <v>3</v>
       </c>
       <c r="J311" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K311" s="4" t="s">
         <v>728</v>
@@ -18401,7 +18395,7 @@
       <c r="B312" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="C312" s="24" t="s">
+      <c r="C312" t="s">
         <v>695</v>
       </c>
       <c r="F312" s="13">
@@ -18414,7 +18408,7 @@
         <v>4</v>
       </c>
       <c r="J312" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K312" s="4" t="s">
         <v>728</v>
@@ -18439,7 +18433,7 @@
       <c r="B313" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="C313" s="24" t="s">
+      <c r="C313" t="s">
         <v>696</v>
       </c>
       <c r="F313" s="13">
@@ -18449,7 +18443,7 @@
         <v>5</v>
       </c>
       <c r="J313" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K313" s="4" t="s">
         <v>728</v>
@@ -18474,7 +18468,7 @@
       <c r="B314" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="C314" s="24" t="s">
+      <c r="C314" t="s">
         <v>697</v>
       </c>
       <c r="F314" s="13">
@@ -18484,7 +18478,7 @@
         <v>6</v>
       </c>
       <c r="J314" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K314" s="4" t="s">
         <v>728</v>
@@ -18509,7 +18503,7 @@
       <c r="B315" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C315" s="24" t="s">
+      <c r="C315" t="s">
         <v>698</v>
       </c>
       <c r="F315" s="13">
@@ -18522,7 +18516,7 @@
         <v>7</v>
       </c>
       <c r="J315" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K315" s="4" t="s">
         <v>728</v>
@@ -18547,7 +18541,7 @@
       <c r="B316" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="C316" s="24" t="s">
+      <c r="C316" t="s">
         <v>699</v>
       </c>
       <c r="F316" s="13">
@@ -18560,7 +18554,7 @@
         <v>8</v>
       </c>
       <c r="J316" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K316" s="4" t="s">
         <v>728</v>
@@ -18585,7 +18579,7 @@
       <c r="B317" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C317" s="24" t="s">
+      <c r="C317" t="s">
         <v>700</v>
       </c>
       <c r="F317" s="13">
@@ -18595,7 +18589,7 @@
         <v>9</v>
       </c>
       <c r="J317" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K317" s="4" t="s">
         <v>728</v>
@@ -18620,7 +18614,7 @@
       <c r="B318" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="C318" s="24" t="s">
+      <c r="C318" t="s">
         <v>701</v>
       </c>
       <c r="F318" s="13">
@@ -18630,7 +18624,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K318" s="4" t="s">
         <v>728</v>
@@ -18655,7 +18649,7 @@
       <c r="B319" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="C319" s="24" t="s">
+      <c r="C319" t="s">
         <v>702</v>
       </c>
       <c r="F319" s="13">
@@ -18668,7 +18662,7 @@
         <v>11</v>
       </c>
       <c r="J319" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K319" s="4" t="s">
         <v>728</v>
@@ -18693,7 +18687,7 @@
       <c r="B320" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="C320" s="24" t="s">
+      <c r="C320" t="s">
         <v>703</v>
       </c>
       <c r="F320" s="13">
@@ -18703,7 +18697,7 @@
         <v>12</v>
       </c>
       <c r="J320" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K320" s="4" t="s">
         <v>728</v>
@@ -18728,7 +18722,7 @@
       <c r="B321" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="C321" s="24" t="s">
+      <c r="C321" t="s">
         <v>704</v>
       </c>
       <c r="F321" s="13">
@@ -18741,7 +18735,7 @@
         <v>13</v>
       </c>
       <c r="J321" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K321" s="4" t="s">
         <v>728</v>
@@ -18766,7 +18760,7 @@
       <c r="B322" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="C322" s="24" t="s">
+      <c r="C322" t="s">
         <v>705</v>
       </c>
       <c r="F322" s="13">
@@ -18779,7 +18773,7 @@
         <v>14</v>
       </c>
       <c r="J322" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K322" s="4" t="s">
         <v>728</v>
@@ -18804,7 +18798,7 @@
       <c r="B323" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="C323" s="24" t="s">
+      <c r="C323" t="s">
         <v>706</v>
       </c>
       <c r="F323" s="13">
@@ -18815,7 +18809,7 @@
         <v>15</v>
       </c>
       <c r="J323" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K323" s="4" t="s">
         <v>728</v>
@@ -18840,7 +18834,7 @@
       <c r="B324" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="C324" s="24" t="s">
+      <c r="C324" t="s">
         <v>707</v>
       </c>
       <c r="F324" s="13">
@@ -18850,7 +18844,7 @@
         <v>16</v>
       </c>
       <c r="J324" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K324" s="4" t="s">
         <v>728</v>
@@ -18875,7 +18869,7 @@
       <c r="B325" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="C325" s="24" t="s">
+      <c r="C325" t="s">
         <v>708</v>
       </c>
       <c r="F325" s="13">
@@ -18888,7 +18882,7 @@
         <v>17</v>
       </c>
       <c r="J325" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K325" s="4" t="s">
         <v>728</v>
@@ -18913,7 +18907,7 @@
       <c r="B326" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="C326" s="24" t="s">
+      <c r="C326" t="s">
         <v>709</v>
       </c>
       <c r="F326" s="13">
@@ -18923,7 +18917,7 @@
         <v>18</v>
       </c>
       <c r="J326" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K326" s="4" t="s">
         <v>728</v>
@@ -18948,7 +18942,7 @@
       <c r="B327" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="C327" s="24" t="s">
+      <c r="C327" t="s">
         <v>731</v>
       </c>
       <c r="F327" s="13">
@@ -18986,7 +18980,7 @@
       <c r="B328" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="C328" s="24" t="s">
+      <c r="C328" t="s">
         <v>732</v>
       </c>
       <c r="F328" s="13">
@@ -19024,7 +19018,7 @@
       <c r="B329" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="C329" s="24" t="s">
+      <c r="C329" t="s">
         <v>733</v>
       </c>
       <c r="F329" s="13">
@@ -19059,7 +19053,7 @@
       <c r="B330" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="C330" s="24" t="s">
+      <c r="C330" t="s">
         <v>734</v>
       </c>
       <c r="F330" s="13">
@@ -19094,7 +19088,7 @@
       <c r="B331" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="C331" s="24" t="s">
+      <c r="C331" t="s">
         <v>735</v>
       </c>
       <c r="F331" s="13">
@@ -19129,7 +19123,7 @@
       <c r="B332" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="C332" s="24" t="s">
+      <c r="C332" t="s">
         <v>736</v>
       </c>
       <c r="F332" s="13">
@@ -19164,7 +19158,7 @@
       <c r="B333" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="C333" s="24" t="s">
+      <c r="C333" t="s">
         <v>737</v>
       </c>
       <c r="F333" s="13">
@@ -19202,7 +19196,7 @@
       <c r="B334" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="C334" s="24" t="s">
+      <c r="C334" t="s">
         <v>738</v>
       </c>
       <c r="F334" s="13">
@@ -19240,7 +19234,7 @@
       <c r="B335" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="C335" s="24" t="s">
+      <c r="C335" t="s">
         <v>739</v>
       </c>
       <c r="F335" s="13">
@@ -19278,7 +19272,7 @@
       <c r="B336" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C336" s="24" t="s">
+      <c r="C336" t="s">
         <v>740</v>
       </c>
       <c r="F336" s="13">
@@ -19313,7 +19307,7 @@
       <c r="B337" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="C337" s="24" t="s">
+      <c r="C337" t="s">
         <v>741</v>
       </c>
       <c r="F337" s="13">
@@ -19351,7 +19345,7 @@
       <c r="B338" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C338" s="24" t="s">
+      <c r="C338" t="s">
         <v>754</v>
       </c>
       <c r="F338" s="13">
@@ -19386,7 +19380,7 @@
       <c r="B339" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="C339" s="24" t="s">
+      <c r="C339" t="s">
         <v>755</v>
       </c>
       <c r="F339" s="13">
@@ -19421,7 +19415,7 @@
       <c r="B340" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="C340" s="24" t="s">
+      <c r="C340" t="s">
         <v>756</v>
       </c>
       <c r="F340" s="13">
@@ -19456,7 +19450,7 @@
       <c r="B341" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="C341" s="24" t="s">
+      <c r="C341" t="s">
         <v>757</v>
       </c>
       <c r="F341" s="13">
@@ -19494,7 +19488,7 @@
       <c r="B342" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C342" s="24" t="s">
+      <c r="C342" t="s">
         <v>758</v>
       </c>
       <c r="F342" s="13">
@@ -19532,7 +19526,7 @@
       <c r="B343" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="C343" s="24" t="s">
+      <c r="C343" t="s">
         <v>759</v>
       </c>
       <c r="F343" s="13">
@@ -19570,7 +19564,7 @@
       <c r="B344" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C344" s="24" t="s">
+      <c r="C344" t="s">
         <v>760</v>
       </c>
       <c r="F344" s="13">
@@ -19605,7 +19599,7 @@
       <c r="B345" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="C345" s="24" t="s">
+      <c r="C345" t="s">
         <v>761</v>
       </c>
       <c r="F345" s="13">
@@ -19643,7 +19637,7 @@
       <c r="B346" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C346" s="24" t="s">
+      <c r="C346" t="s">
         <v>762</v>
       </c>
       <c r="F346" s="13">
@@ -19678,7 +19672,7 @@
       <c r="B347" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="C347" s="24" t="s">
+      <c r="C347" t="s">
         <v>773</v>
       </c>
       <c r="F347" s="13">
@@ -19716,7 +19710,7 @@
       <c r="B348" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="C348" s="24" t="s">
+      <c r="C348" t="s">
         <v>774</v>
       </c>
       <c r="F348" s="13">
@@ -19751,7 +19745,7 @@
       <c r="B349" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C349" s="24" t="s">
+      <c r="C349" t="s">
         <v>775</v>
       </c>
       <c r="F349" s="13">
@@ -19786,7 +19780,7 @@
       <c r="B350" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C350" s="24" t="s">
+      <c r="C350" t="s">
         <v>776</v>
       </c>
       <c r="F350" s="13">
@@ -19824,7 +19818,7 @@
       <c r="B351" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="C351" s="24" t="s">
+      <c r="C351" t="s">
         <v>777</v>
       </c>
       <c r="F351" s="13">
@@ -19859,7 +19853,7 @@
       <c r="B352" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C352" s="24" t="s">
+      <c r="C352" t="s">
         <v>778</v>
       </c>
       <c r="F352" s="13">
@@ -19894,7 +19888,7 @@
       <c r="B353" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="C353" s="24" t="s">
+      <c r="C353" t="s">
         <v>779</v>
       </c>
       <c r="F353" s="13">
@@ -19929,7 +19923,7 @@
       <c r="B354" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="C354" s="24" t="s">
+      <c r="C354" t="s">
         <v>780</v>
       </c>
       <c r="F354" s="13">
@@ -19964,7 +19958,7 @@
       <c r="B355" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="C355" s="24" t="s">
+      <c r="C355" t="s">
         <v>781</v>
       </c>
       <c r="F355" s="13">
@@ -19999,7 +19993,7 @@
       <c r="B356" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="C356" s="24" t="s">
+      <c r="C356" t="s">
         <v>791</v>
       </c>
       <c r="F356" s="13">
@@ -20034,7 +20028,7 @@
       <c r="B357" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="C357" s="24" t="s">
+      <c r="C357" t="s">
         <v>792</v>
       </c>
       <c r="F357" s="13">
@@ -20069,7 +20063,7 @@
       <c r="B358" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="C358" s="24" t="s">
+      <c r="C358" t="s">
         <v>793</v>
       </c>
       <c r="F358" s="13">
@@ -20104,7 +20098,7 @@
       <c r="B359" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="C359" s="24" t="s">
+      <c r="C359" t="s">
         <v>794</v>
       </c>
       <c r="F359" s="13">
@@ -20142,7 +20136,7 @@
       <c r="B360" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="C360" s="24" t="s">
+      <c r="C360" t="s">
         <v>795</v>
       </c>
       <c r="F360" s="13">
@@ -20177,7 +20171,7 @@
       <c r="B361" s="4" t="s">
         <v>801</v>
       </c>
-      <c r="C361" s="24" t="s">
+      <c r="C361" t="s">
         <v>803</v>
       </c>
       <c r="F361" s="13">
@@ -20212,7 +20206,7 @@
       <c r="B362" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C362" s="24" t="s">
+      <c r="C362" t="s">
         <v>804</v>
       </c>
       <c r="F362" s="13">
@@ -20247,7 +20241,7 @@
       <c r="B363" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="C363" s="24" t="s">
+      <c r="C363" t="s">
         <v>805</v>
       </c>
       <c r="F363" s="13">
@@ -20285,7 +20279,7 @@
       <c r="B364" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="C364" s="24" t="s">
+      <c r="C364" t="s">
         <v>806</v>
       </c>
       <c r="F364" s="13">
@@ -20320,7 +20314,7 @@
       <c r="B365" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="C365" s="24" t="s">
+      <c r="C365" t="s">
         <v>807</v>
       </c>
       <c r="F365" s="13">
@@ -20355,7 +20349,7 @@
       <c r="B366" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="C366" s="24" t="s">
+      <c r="C366" t="s">
         <v>808</v>
       </c>
       <c r="F366" s="13">
@@ -20390,7 +20384,7 @@
       <c r="B367" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="C367" s="24" t="s">
+      <c r="C367" t="s">
         <v>809</v>
       </c>
       <c r="F367" s="13">
@@ -20425,7 +20419,7 @@
       <c r="B368" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="C368" s="24" t="s">
+      <c r="C368" t="s">
         <v>810</v>
       </c>
       <c r="F368" s="13">
@@ -20460,7 +20454,7 @@
       <c r="B369" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="C369" s="24" t="s">
+      <c r="C369" t="s">
         <v>820</v>
       </c>
       <c r="F369" s="13">
@@ -20495,7 +20489,7 @@
       <c r="B370" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="C370" s="24" t="s">
+      <c r="C370" t="s">
         <v>821</v>
       </c>
       <c r="F370" s="13">
@@ -20533,7 +20527,7 @@
       <c r="B371" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="C371" s="24" t="s">
+      <c r="C371" t="s">
         <v>822</v>
       </c>
       <c r="F371" s="13">
@@ -20571,7 +20565,7 @@
       <c r="B372" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="C372" s="24" t="s">
+      <c r="C372" t="s">
         <v>823</v>
       </c>
       <c r="F372" s="13">
@@ -20609,7 +20603,7 @@
       <c r="B373" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="C373" s="30" t="s">
+      <c r="C373" s="27" t="s">
         <v>824</v>
       </c>
       <c r="F373" s="13">
@@ -20647,7 +20641,7 @@
       <c r="B374" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="C374" s="24" t="s">
+      <c r="C374" t="s">
         <v>825</v>
       </c>
       <c r="F374" s="13">
@@ -20685,7 +20679,7 @@
       <c r="B375" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="C375" s="24" t="s">
+      <c r="C375" t="s">
         <v>835</v>
       </c>
       <c r="F375" s="13">
@@ -20723,7 +20717,7 @@
       <c r="B376" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="C376" s="24" t="s">
+      <c r="C376" t="s">
         <v>836</v>
       </c>
       <c r="F376" s="13">
@@ -20761,7 +20755,7 @@
       <c r="B377" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="C377" s="24" t="s">
+      <c r="C377" t="s">
         <v>837</v>
       </c>
       <c r="F377" s="13">
@@ -20799,7 +20793,7 @@
       <c r="B378" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="C378" s="24" t="s">
+      <c r="C378" t="s">
         <v>838</v>
       </c>
       <c r="F378" s="13">
@@ -20837,7 +20831,7 @@
       <c r="B379" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="C379" s="24" t="s">
+      <c r="C379" t="s">
         <v>839</v>
       </c>
       <c r="F379" s="13">
@@ -20875,7 +20869,7 @@
       <c r="B380" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C380" s="31" t="s">
+      <c r="C380" t="s">
         <v>840</v>
       </c>
       <c r="F380" s="13">
@@ -20913,7 +20907,7 @@
       <c r="B381" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="C381" s="24" t="s">
+      <c r="C381" t="s">
         <v>848</v>
       </c>
       <c r="F381" s="13">
@@ -20951,7 +20945,7 @@
       <c r="B382" s="4" t="s">
         <v>853</v>
       </c>
-      <c r="C382" s="24" t="s">
+      <c r="C382" t="s">
         <v>849</v>
       </c>
       <c r="F382" s="13">
@@ -20989,7 +20983,7 @@
       <c r="B383" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="C383" s="24" t="s">
+      <c r="C383" t="s">
         <v>850</v>
       </c>
       <c r="F383" s="13">
@@ -21027,7 +21021,7 @@
       <c r="B384" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="C384" s="24" t="s">
+      <c r="C384" t="s">
         <v>851</v>
       </c>
       <c r="F384" s="13">
@@ -21065,7 +21059,7 @@
       <c r="B385" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="C385" s="30" t="s">
+      <c r="C385" s="27" t="s">
         <v>852</v>
       </c>
       <c r="F385" s="13">
@@ -21103,7 +21097,7 @@
       <c r="B386" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="C386" s="24" t="s">
+      <c r="C386" t="s">
         <v>858</v>
       </c>
       <c r="F386" s="13">
@@ -21138,7 +21132,7 @@
       <c r="B387" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="C387" s="24" t="s">
+      <c r="C387" t="s">
         <v>859</v>
       </c>
       <c r="F387" s="13">
@@ -21173,7 +21167,7 @@
       <c r="B388" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="C388" s="24" t="s">
+      <c r="C388" t="s">
         <v>860</v>
       </c>
       <c r="F388" s="13">
@@ -21211,7 +21205,7 @@
       <c r="B389" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="C389" s="24" t="s">
+      <c r="C389" t="s">
         <v>861</v>
       </c>
       <c r="F389" s="13">
@@ -21249,7 +21243,7 @@
       <c r="B390" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="C390" s="24" t="s">
+      <c r="C390" t="s">
         <v>862</v>
       </c>
       <c r="F390" s="13">
@@ -21284,7 +21278,7 @@
       <c r="B391" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="C391" s="24" t="s">
+      <c r="C391" t="s">
         <v>863</v>
       </c>
       <c r="F391" s="13">
@@ -21322,7 +21316,7 @@
       <c r="B392" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="C392" s="24" t="s">
+      <c r="C392" t="s">
         <v>864</v>
       </c>
       <c r="F392" s="13">
@@ -21360,7 +21354,7 @@
       <c r="B393" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="C393" s="24" t="s">
+      <c r="C393" t="s">
         <v>865</v>
       </c>
       <c r="F393" s="13">
@@ -21398,7 +21392,7 @@
       <c r="B394" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="C394" s="30" t="s">
+      <c r="C394" s="27" t="s">
         <v>866</v>
       </c>
       <c r="F394" s="13">
@@ -21436,7 +21430,7 @@
       <c r="B395" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="C395" s="24" t="s">
+      <c r="C395" t="s">
         <v>867</v>
       </c>
       <c r="F395" s="13">
@@ -21474,7 +21468,7 @@
       <c r="B396" s="4" t="s">
         <v>885</v>
       </c>
-      <c r="C396" s="24" t="s">
+      <c r="C396" t="s">
         <v>878</v>
       </c>
       <c r="F396" s="13">
@@ -21509,7 +21503,7 @@
       <c r="B397" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="C397" s="24" t="s">
+      <c r="C397" t="s">
         <v>879</v>
       </c>
       <c r="F397" s="13">
@@ -21544,7 +21538,7 @@
       <c r="B398" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="C398" s="24" t="s">
+      <c r="C398" t="s">
         <v>880</v>
       </c>
       <c r="F398" s="13">
@@ -21582,7 +21576,7 @@
       <c r="B399" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="C399" s="24" t="s">
+      <c r="C399" t="s">
         <v>881</v>
       </c>
       <c r="F399" s="13">
@@ -21620,7 +21614,7 @@
       <c r="B400" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="C400" s="24" t="s">
+      <c r="C400" t="s">
         <v>882</v>
       </c>
       <c r="F400" s="13">
@@ -21658,7 +21652,7 @@
       <c r="B401" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="C401" s="24" t="s">
+      <c r="C401" t="s">
         <v>883</v>
       </c>
       <c r="F401" s="13">
@@ -21693,7 +21687,7 @@
       <c r="B402" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="C402" s="24" t="s">
+      <c r="C402" t="s">
         <v>884</v>
       </c>
       <c r="F402" s="13">
@@ -21731,7 +21725,7 @@
       <c r="B403" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="C403" s="24" t="s">
+      <c r="C403" t="s">
         <v>894</v>
       </c>
       <c r="F403" s="13">
@@ -21766,7 +21760,7 @@
       <c r="B404" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="C404" s="24" t="s">
+      <c r="C404" t="s">
         <v>896</v>
       </c>
       <c r="F404" s="13">
@@ -21801,7 +21795,7 @@
       <c r="B405" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="C405" s="24" t="s">
+      <c r="C405" t="s">
         <v>897</v>
       </c>
       <c r="F405" s="13">
@@ -21836,7 +21830,7 @@
       <c r="B406" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C406" s="24" t="s">
+      <c r="C406" t="s">
         <v>898</v>
       </c>
       <c r="F406" s="13">
@@ -21871,7 +21865,7 @@
       <c r="B407" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="C407" s="24" t="s">
+      <c r="C407" t="s">
         <v>899</v>
       </c>
       <c r="F407" s="13">
@@ -21909,7 +21903,7 @@
       <c r="B408" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C408" s="32" t="s">
+      <c r="C408" s="28" t="s">
         <v>906</v>
       </c>
       <c r="F408" s="13">
@@ -21944,7 +21938,7 @@
       <c r="B409" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="C409" s="24" t="s">
+      <c r="C409" t="s">
         <v>907</v>
       </c>
       <c r="F409" s="13">
@@ -21982,7 +21976,7 @@
       <c r="B410" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="C410" s="24" t="s">
+      <c r="C410" t="s">
         <v>908</v>
       </c>
       <c r="F410" s="13">
@@ -22017,7 +22011,7 @@
       <c r="B411" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="C411" s="24" t="s">
+      <c r="C411" t="s">
         <v>909</v>
       </c>
       <c r="F411" s="13">
@@ -22052,7 +22046,7 @@
       <c r="B412" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="C412" s="30" t="s">
+      <c r="C412" s="27" t="s">
         <v>910</v>
       </c>
       <c r="F412" s="13">
